--- a/ConfigExporter/xlsx/duel_byoyomi_count.xlsx
+++ b/ConfigExporter/xlsx/duel_byoyomi_count.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -437,6 +437,11 @@
           <t>读秒次数</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>OGS启用</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -454,6 +459,11 @@
           <t>count</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ogsEnabled</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -471,6 +481,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -488,6 +503,11 @@
           <t>#require</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -503,6 +523,11 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -518,6 +543,11 @@
       <c r="C6" t="n">
         <v>1</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -533,6 +563,11 @@
       <c r="C7" t="n">
         <v>3</v>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -547,6 +582,11 @@
       </c>
       <c r="C8" t="n">
         <v>5</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/ConfigExporter/xlsx/duel_byoyomi_count.xlsx
+++ b/ConfigExporter/xlsx/duel_byoyomi_count.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -552,16 +552,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3次</t>
+          <t>2次</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -572,18 +572,158 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3次</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4次</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>5次</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C10" t="n">
         <v>5</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>6次</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7次</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>8次</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>9次</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>9</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10次</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>True</t>
         </is>
